--- a/data/raw/附件 1 市主城区 10 个典型区域基础数据.xlsx
+++ b/data/raw/附件 1 市主城区 10 个典型区域基础数据.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="附件 1 延安市主城区 10 个典型区域基础数据" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>区域编号</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>区域电网总容量（万千瓦）</t>
-  </si>
-  <si>
-    <t>数据基于市 2025 年实际测算，快充桩按 120kW 直流双枪标准，慢充桩按 7kW 交流桩标准</t>
   </si>
 </sst>
 </file>
@@ -1219,17 +1216,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="18.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.8727272727273" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.8727272727273" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.8727272727273" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.8727272727273" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.8727272727273" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.2545454545455" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6272727272727" style="1" customWidth="1"/>
     <col min="11" max="11" width="24" style="1" customWidth="1"/>
     <col min="12" max="14" width="9" style="1"/>
   </cols>
@@ -1586,10 +1583,8 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="14" spans="4:4">
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
+    <row r="14" spans="1:10">
+      <c r="D14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
